--- a/reports/Debug-purgatory-20260104/For Winter Ending (Actual)_Revenue.xlsx
+++ b/reports/Debug-purgatory-20260104/For Winter Ending (Actual)_Revenue.xlsx
@@ -106,10 +106,10 @@
     <t>D3000</t>
   </si>
   <si>
-    <t xml:space="preserve">D4053                    </t>
-  </si>
-  <si>
-    <t>D4054</t>
+    <t>D4053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D4054                    </t>
   </si>
   <si>
     <t>D4055</t>
@@ -121,7 +121,7 @@
     <t>D5201</t>
   </si>
   <si>
-    <t>D5202</t>
+    <t xml:space="preserve">D5202                    </t>
   </si>
   <si>
     <t xml:space="preserve">D5205                    </t>
